--- a/Controle_/Acessos GTCON.xlsx
+++ b/Controle_/Acessos GTCON.xlsx
@@ -5267,7 +5267,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>elaine@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>df30@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5291,7 +5291,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>df31@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5303,7 +5303,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>df8@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>df4@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5375,7 +5375,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>atendimento4@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5411,7 +5411,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>dc10@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>contabil.rj@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>dp15@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5471,7 +5471,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>dp5@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5487,7 +5487,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IMPLANTACAO DP</t>
+          <t>IMPLANTAÇÃO DP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -5507,7 +5507,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E-MAIL VAGO</t>
+          <t>implantacao3@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">

--- a/Controle_/Acessos GTCON.xlsx
+++ b/Controle_/Acessos GTCON.xlsx
@@ -5312,17 +5312,12 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>COMPLIANCE</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5348,17 +5343,12 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>ATENDIMENTO</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5384,17 +5374,12 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>CONTABIL</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5432,17 +5417,12 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>DP</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5480,17 +5460,12 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>IMPLANTAÇÃO DP</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6187,612 +6162,579 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="39" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="13.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emanuela </t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1607251811</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dp3@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Efg149375&amp;</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Emanuela </t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1607251811</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>dp3@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gabriella</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>512261603</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dp.1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>R!816723436344on</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Josimara Alves</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1007205611</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dp10@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Z#876179077002af</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Karina Alves</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1514474252</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dp12@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>X(420695250462at</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>25130710Fa@</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lidiane Oliveira</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>597358922</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dp16@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gtcon#2025</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Livia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>626237333</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dp2@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>T#eC@1882</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Efg149375&amp;</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Gabriella</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>512261603</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>dp.1@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="G7" t="n">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luísa </t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1876934276</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dp14@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>R!816723436344on</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Q)904672906240ux</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Josimara Alves</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1007205611</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>dp10@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luiz Gustavo </t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>493882728</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dp21@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Z#876179077002af</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>G%367822712641ar</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Monique</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1478923107</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dp17@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>H$975428139147ot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Raphaela</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1555081951</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dp7@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gtcon#2025*</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Thais</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>997159970</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dp11@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Z$707010893181az</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>1234</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Karina Alves</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1514474252</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>dp12@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Vivian</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1803850864</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>departamentopessoal@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>X(420695250462at</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Q.092954551838uz</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>25130710Fa@</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Lidiane Oliveira</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>597358922</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>dp16@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2025</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lorran </t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1607251811</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dp13@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>N$049996617795ub</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Livia</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>626237333</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>dp2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luísa </t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>1876934276</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>dp14@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Q)904672906240ux</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Luiz Gustavo </t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>493882728</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>dp21@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>G%367822712641ar</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Monique</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1478923107</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>dp17@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>H$975428139147ot</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Raphaela</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1555081951</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>dp7@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2025*</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Thais</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>997159970</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>dp11@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>Z$707010893181az</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Vivian</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1803850864</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>departamentopessoal@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>Q.092954551838uz</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lorran </t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1607251811</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>dp13@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>N$049996617795ub</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ROMULO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>ROMULO</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="32" t="n"/>
-      <c r="F17" s="32" t="n"/>
-      <c r="G17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>SENHA ANYDESK</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SENHA UNICO </t>
-        </is>
-      </c>
-      <c r="F18" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>569215440</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>569215440</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>administrativo1@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Rdestac25</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>GTCON</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>F*415203413144ot</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="mailto:dp10@grupoteccon.com.br" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="mailto:dp12@grupoteccon.com.br" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="mailto:dp7@grupoteccon.com.br" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" display="mailto:dp11@grupoteccon.com.br" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId10"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/Controle_/Acessos GTCON.xlsx
+++ b/Controle_/Acessos GTCON.xlsx
@@ -28,7 +28,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ACESSOS SERVIDOR'!$A$1:$B$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'CS'!$A$2:$G$2</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -2088,97 +2087,110 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="18.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="9.85546875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="2.7109375" customWidth="1" min="8" max="8"/>
-    <col width="23" bestFit="1" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>COMPLIANCE</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
-      <c r="I1" s="10" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Barbara Oliveira</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1339292647</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>df24@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B%014362724844uy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Barbara Oliveira</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1339292647</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>df24@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+          <t>Edlian</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1508174447</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>compliance1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>B%014362724844uy</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K#626172737664oz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2188,508 +2200,464 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GTCON25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Edlian</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1508174447</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>compliance1@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+          <t>Marcos Mateus</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1759579173</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nit4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>V*243668666737og</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rose Bahia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1737402030</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>legalizacao2@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>K#626172737664oz</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7456</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Thamires Cristiny</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1862420260</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>legalizacao@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Marcos Mateus</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1759579173</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>nit4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>V*243668666737og</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Rose Bahia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1737402030</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>legalizacao2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>7456</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Thamires Cristiny</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1862420260</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>legalizacao@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="0" tint="-0.3499862666707358"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="31.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="10.140625" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>LEGALIZAÇÃO</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MAQUINA PESSOAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>legalizacao3@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>X!969714593839ak</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Danilo</t>
+          <t>Ilsa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MAQUINA PESSOAL</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>legalizacao3@gtconbrasil.com.br</t>
+          <t>1252954579</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ilsa@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>X!969714593839ak</t>
+          <t>Gtcon#2025*</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ilsa@1978</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Ilsa</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>1252954579</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ilsa@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2025*</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1527870876</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>legalizacao4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thamires Sant'Anna</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>817419339</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>legalizacao1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M&amp;256971996970ub</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Thb2038</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vinicius</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1792849659</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>legalizacao5@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>T#eC@1882</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>ilsa@1978</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Ryan</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1527870876</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>legalizacao4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Thamires Sant'Anna</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>817419339</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>legalizacao1@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>M&amp;256971996970ub</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Thb2038</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Vinicius</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1792849659</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>legalizacao5@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="mailto:ilsa@grupoteccon.com.br" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="18.7109375" defaultRowHeight="15"/>
-  <cols>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="37.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="18.28515625" bestFit="1" customWidth="1" style="5" min="7" max="7"/>
-    <col width="3.7109375" customWidth="1" min="8" max="8"/>
-  </cols>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>TRIBUTARIO</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alexandre</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1766494962</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tributario6@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Q)894582964511ul</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Alexandre</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1766494962</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>tributario6@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Danielle</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1385188559</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>tributario7@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Q)894582964511ul</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>F#070746237821ud</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2697,7 +2665,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2706,25 +2674,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Danielle</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1385188559</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>tributario7@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+          <t>Gabriela</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1314578134</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>tributario3@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>F#070746237821ud</t>
+          <t>K#884715151179av</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2732,7 +2702,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2741,25 +2711,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gabriela</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1314578134</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>tributario3@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
+          <t>Ivine</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1077971141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>tributario2@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>K#884715151179av</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>V/249346609603ay</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2767,34 +2739,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GTCON25?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Ivine</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1077971141</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>tributario2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lorrane</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1556232617</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>correspondente10@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>V/249346609603ay</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2802,34 +2776,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25?</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Lorrane</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1556232617</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>correspondente10@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1680423137</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>tributario4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>H&amp;440909264741ud</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2837,199 +2813,166 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Pedro</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>1680423137</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>tributario4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>H&amp;440909264741ud</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tributário</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>tributario@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y*105927186843uy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tributário</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>tributario@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Y*105927186843uy</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" s="2" t="n"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" display="mailto:tributario3@grupoteccon.com.br" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" display="mailto:tributario2@grupoteccon.com.br" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" display="mailto:tributario4@grupoteccon.com.br" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="mailto:tributario@grupoteccon.com.br" r:id="rId6"/>
-  </hyperlinks>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="0" tint="-0.3499862666707358"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col width="15.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="38.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="20.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="9.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SUCESSO DO CLIEINTE </t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bruna Marques </t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1669260100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>implantacao6@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K/352410472767ub</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bruna Marques </t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1669260100</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>implantacao6@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1164572232</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cs2@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>K/352410472767ub</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B$022390897391ot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NÃO UTILIZA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3041,90 +2984,96 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gabriel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1164572232</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>cs2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+          <t>Paloma</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1576234925</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cs4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>B$022390897391ot</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P*164407148156ut</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>NÃO UTILIZA</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paloma</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1576234925</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>cs4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
+          <t>Reinaldo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1465051328</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cs3@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>P*164407148156ut</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y@178585603705ax</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>NÃO UTILIZA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reinaldo</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1465051328</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>cs3@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
+          <t>Rogerio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1524611291</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cs1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Y@178585603705ax</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M.557258335913oh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3132,34 +3081,36 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Rogerio</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>1524611291</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>cs1@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Thainá</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1293063279</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cs@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>M.557258335913oh</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Q&amp;867629947214am</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3167,148 +3118,114 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Thainá</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1293063279</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>cs@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Q&amp;867629947214am</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NÃO UTILIZA</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G2">
-    <sortState ref="A3:G8">
-      <sortCondition ref="A2"/>
-    </sortState>
-  </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>MARKETING</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Arthur</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1459397918</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>marketing5@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>F$258667134783ot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NÃO UTILIZA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arthur</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1459397918</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>marketing5@gtconbrasil.com.br</t>
+          <t>Denise</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1789461031</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>marketing2@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3316,9 +3233,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>F$258667134783ot</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>X&amp;855400399596ad</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3326,24 +3243,26 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Denise</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>1789461031</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>marketing2@gtconbrasil.com.br</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gabriel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>marketing4@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3351,9 +3270,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>X&amp;855400399596ad</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3361,26 +3280,26 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>and@87412</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Italo Senna</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>marketing4@gtconbrasil.com.br</t>
+          <t>1567075019</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sucessodocliente@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3388,7 +3307,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>T#eC@1881</t>
         </is>
@@ -3398,24 +3317,26 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>and@87412</t>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>marketing2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Italo Senna</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>1567075019</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>sucessodocliente@gtconbrasil.com.br</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>625106930</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>marketing@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3423,61 +3344,63 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>T#eC@5202</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NÃO UTILIZA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>marketing6@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>T#eC@1881</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>marketing2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Leandro</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>625106930</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>marketing@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@5202</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NÃO UTILIZA</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Wellington Oliveira</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3485,9 +3408,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>marketing6@gtconbrasil.com.br</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cs.nayra@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3495,9 +3418,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y(187889266381ow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3505,59 +3428,14 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wellington Oliveira</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>cs.nayra@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Y(187889266381ow</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NÃO UTILIZA</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>PESSOAL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" display="mailto:marketing2@grupoteccon.com.br" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" location="eC@5202" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4000,90 +3878,81 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="34" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="20.140625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" min="6" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>ANYDESK</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>E-MAIL</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>ONEDRIVE</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
-        <is>
-          <t>SENHA MAQUINA</t>
-        </is>
-      </c>
-      <c r="G1" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ONVIO </t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Boletos GTCON</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>boletos@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bol@1882</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4095,12 +3964,12 @@
           <t>Compliance</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>compliance@gtconbrasil.com.br</t>
         </is>
@@ -4127,74 +3996,74 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Contas Gtcon</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>contas@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>B*948487783131al</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Contato Gtcon</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>contato@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>X&amp;714260775410ux</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4206,7 +4075,8 @@
           <t>Dominio</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>adm.dominio@gtconbrasil.com.br</t>
         </is>
@@ -4233,17 +4103,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Gmail Tecnologia</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>tecnologia.gtcon@gmail.com</t>
         </is>
@@ -4253,7 +4123,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Gtcon@2024</t>
         </is>
@@ -4263,7 +4133,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4280,7 +4150,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ibge@gtconbrasil.com.br</t>
         </is>
@@ -4307,98 +4177,102 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Sala Reuniao JF</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>reuniao@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>T(540185726880oy</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Sala Reuniao RJ</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>1017859196</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1017859196</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>reuniaorj@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Gtcon#2025</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>T#eC@1881</t>
         </is>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>2210</v>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Onvio/G-click | Integração</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>integracaogclick@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>G#830834686195oj</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4410,17 +4284,7 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="mailto:tecnologia.gtcon@gmail.com" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -6678,27 +6542,12 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>ROMULO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6731,7 +6580,6 @@
           <t>F*415203413144ot</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6741,442 +6589,480 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="0" tint="-0.3499862666707358"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="26.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="22.7109375" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="23" bestFit="1" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>FISCAL</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
-      <c r="I1" s="10" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alexsandra</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1776962191</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>df15@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N&amp;057477143456uc</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GTCON#25</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Alexsandra</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1776962191</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>df15@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ana Cristina </t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1297620606</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>df21@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gtcon@2025*</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1081122991</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>df35@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>N&amp;057477143456uc</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>W@610892260033ov</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bruna</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1223833876</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> df19@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>N/128228075657ax</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GTCON25?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bruno Silva</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1637522369</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>df17@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>H)355399053560ay</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Caroline Pereira</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1391277951</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>df18@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gtcon@#2025*</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N$840579634343aj</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>GTCON#25</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ana Cristina </t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1297620606</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>df21@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon@2025*</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Diego da Silva</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1007587701</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>df11@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Diego1988</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Elaine Braz</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>258825234</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>df3@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>T#eC@1882</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>131874</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fabiana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1907114823</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>df23@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1081122991</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>df35@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gislaine Lopes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1738315913</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>df5@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>W@610892260033ov</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Bruna</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>1223833876</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> df19@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L^880875925287uj</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1664432245</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>correspondente15@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>N/128228075657ax</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25?</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Bruno Silva</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1637522369</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>df17@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>H)355399053560ay</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Q*674758686522oh</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Caroline Pereira</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>1391277951</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>df18@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon@#2025*</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>N$840579634343aj</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>GTCON#25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Diego da Silva</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1007587701</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>df11@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Diego1988</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Elaine Braz</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>258825234</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>df3@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>131874</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Fabiana</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>1907114823</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>df23@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Gislaine Lopes</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>1738315913</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>df5@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>L^880875925287uj</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jean</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1664432245</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>correspondente15@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
+          <t xml:space="preserve">João Gabriel </t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1190397908</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>df22@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>Q*674758686522oh</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>T(072167316240ul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7184,7 +7070,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
@@ -7193,25 +7079,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">João Gabriel </t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1190397908</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>df22@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1679828269</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>df27@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>T(072167316240ul</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7219,67 +7107,68 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>25122871</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Jonathan</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1679828269</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>df27@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Katia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1156498952</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>df26@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>G*429581463622ux</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>25122871</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Katia</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1156498952</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>df26@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
+          <t>Kivea</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1802943923</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>df9@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>G*429581463622ux</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>H$052205583716up</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7287,29 +7176,36 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Kivea</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1802943923</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>df9@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Larissa Caroline </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>274266045</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>df2@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>H$052205583716up</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7317,277 +7213,295 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>99360873</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1658225062</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>df34@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>T^936542112128ov</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lucas Delgado</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>211502015</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>df33@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>C$434889373778am</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Larissa Caroline </t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>274266045</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>df2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Luis Gustavo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1322386127</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>df20@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>B&amp;773115114389oh</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lukas </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1948950881</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>df6@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>T*354852881253as</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mariana</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1872564945</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>df16@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>R&amp;457869079673us</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GTCON</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mariane Ribeiro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1812549024</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>supervisaodf@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>X&amp;520526444287ug</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michele </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1630099813</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>df1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>T#eC@1882</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>99360873</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Leandro</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1658225062</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>df34@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>440262mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Waleska</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1457296663</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>df7@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>T^936542112128ov</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Lucas Delgado</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>211502015</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>df33@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>C$434889373778am</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Luis Gustavo</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1322386127</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>df20@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>B&amp;773115114389oh</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lukas </t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1948950881</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>df6@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>T*354852881253as</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Mariana</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1872564945</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>df16@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>R&amp;457869079673us</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>GTCON</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Mariane Ribeiro</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>1812549024</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>supervisaodf@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>X&amp;520526444287ug</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Michele </t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1630099813</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>df1@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>G&amp;094151887325ad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7595,166 +7509,124 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>440262mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Waleska</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1457296663</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>df7@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>G&amp;094151887325ad</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>GTCON25?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="mailto:df17@gtconbrasil.com.br" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" display="mailto:df11@grupoteccon.com.br" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="mailto:df5@grupoteccon.com.br" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" display="mailto:df16@gtconbrasil.com.br" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" display="mailto:supervisaodf@grupoteccon.com.br" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" display="mailto:df1@grupoteccon.com.br" r:id="rId18"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="17.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="35.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="20.140625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>CONTABIL</t>
-        </is>
-      </c>
-      <c r="B1" s="33" t="n"/>
-      <c r="C1" s="33" t="n"/>
-      <c r="D1" s="33" t="n"/>
-      <c r="E1" s="33" t="n"/>
-      <c r="F1" s="33" t="n"/>
-      <c r="G1" s="33" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alessandra </t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1954967762</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dc1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>K#799763156243uz</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alessandra </t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1954967762</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>dc1@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alexandre Vieira</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>535291066</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>dc5@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>K#799763156243uz</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7762,139 +7634,147 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>03122005</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Allan</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>569215440</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dc31@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Gtcon@2024*</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T%808238945694us</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Alexandre Vieira</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>535291066</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>dc5@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Clara Aleixo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1252954579</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>dc29@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gtcon#26</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>X$453741082475ax</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cla216124@</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>807385438</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dc3@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>03122005</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Allan</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>569215440</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>dc31@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon@2024*</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>T%808238945694us</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>B)795949908528ux</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Clara Aleixo</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1252954579</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>dc29@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gtcon#26</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>X$453741082475ax</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Cla216124@</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>807385438</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>dc3@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1940189047</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>dc27@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>B)795949908528ux</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7902,139 +7782,147 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>GTCON</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Higor Souza</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1110511407</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>correspondente14@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Q@373078677901aj</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jhonatan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1598055607</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dc24@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>D&amp;752282126324od</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Gabrielle</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1940189047</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>dc27@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>987005640</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>dc7@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>GTCON</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Higor Souza</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>1110511407</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>correspondente14@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>N.477538729076ah</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lucas Ferreira </t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1595622594</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>dc11@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Q@373078677901aj</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Jhonatan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1598055607</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>dc24@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>D&amp;752282126324od</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Kevin</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>987005640</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>dc7@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>N.477538729076ah</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>P#969992867506ap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8042,7 +7930,7 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
@@ -8051,163 +7939,175 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lucas Ferreira </t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1595622594</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>dc11@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
+          <t>Marcelle Cabral</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>496882501</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dc21@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gtcon@2025*</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L%396292469450ub</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Marcia Foffano</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1978578439</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dc9@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>P#969992867506ap</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>marcia</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mateus Arruda</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1060092529</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dc13@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>M%007895756312uw</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>16109040</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Mayara Ferreira</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1126653487</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dc22@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gtcon2025#</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gtcon#2025*</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Marcelle Cabral</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>496882501</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>dc21@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon@2025*</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>L%396292469450ub</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Marcia Foffano</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1978578439</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>dc9@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>marcia</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Mateus Arruda</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1060092529</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>dc13@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>M%007895756312uw</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>16109040</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mayara Ferreira</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1126653487</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>dc22@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon2025#</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2025*</t>
+          <t>Maycon Gil Ferreira</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1205311230</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dc8@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8215,209 +8115,221 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Mg91539877</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Miguel Guimarães</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1159617120</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dc17@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>miguell10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Roberta</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1615957552</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dc16@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>J#026079261080av</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>818235168</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>correspondente13@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Y*594022779280am</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Maycon Gil Ferreira</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1205311230</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>dc8@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Thais</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>310710390</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>dc26@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Mg91539877</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Miguel Guimarães</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1159617120</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>dc17@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Q)217740829082aq</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thais Amaral</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1631603146</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dc20@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>miguell10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Roberta</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1615957552</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>dc16@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>G/007220886145ux</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Thiago Almeida</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>341667537</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dc28@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>J#026079261080av</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Rute</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>818235168</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>correspondente13@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>Y*594022779280am</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Thais</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>310710390</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>dc26@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>Q)217740829082aq</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Thais Amaral</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1631603146</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>dc20@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>G/007220886145ux</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>D@752170480543ab</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8425,34 +8337,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GTCON</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Thiago Almeida</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>341667537</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>dc28@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>D@752170480543ab</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Thiago Nunes</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1692099423</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nit1@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Gtcon#2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Z*547528746981uh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8460,69 +8374,73 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>GTCON</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thiago Nunes</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1692099423</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>nit1@gtconbrasil.com.br</t>
+          <t>Thiago Panio</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1056345588</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dc19@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gtcon#2026</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>Z*547528746981uh</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>G.184920791643ow.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GTCON25</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Thiago Panio</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1056345588</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>dc19@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Verônica</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>331011180</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dc4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>G.184920791643ow.</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8530,34 +8448,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1420</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Verônica</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>331011180</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>dc4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Wesley Magalhães</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1880953177</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>dc6@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GtconBrasil@2024</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Z@801533563849um</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8565,304 +8485,219 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Wesley Magalhães</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1880953177</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>dc6@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>GtconBrasil@2024</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>Z@801533563849um</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>908030</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>908030</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EXTERNO</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>EXTERNO</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="32" t="n"/>
-      <c r="D29" s="32" t="n"/>
-      <c r="E29" s="32" t="n"/>
-      <c r="F29" s="32" t="n"/>
-      <c r="G29" s="32" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D30" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E30" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Tatiane</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Q^518391560283uv</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:G29"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" display="mailto:dc13@grupoteccon.com.br" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" display="mailto:dc17@grupoteccon.com.br" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" display="mailto:dc16@grupoteccon.com.br" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId16"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="0" tint="-0.3499862666707358"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="24" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>IMPLANTAÇÃO DOMINIO</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="n"/>
-      <c r="C1" s="32" t="n"/>
-      <c r="D1" s="32" t="n"/>
-      <c r="E1" s="32" t="n"/>
-      <c r="F1" s="32" t="n"/>
-      <c r="G1" s="32" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Dandara</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1188916023</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1188916023</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>nit7@gtconbrasil.com.br</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>V)890597560774uj</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IMPLANTAÇÃO FISCAL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>IMPLANTAÇÃO FISCAL</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Glasiane</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>845685380</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>df12@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>X^743816816092oc</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>SCI</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joao </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1371400479</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>tributario5@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>D.983222139855od</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>123456</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Glasiane</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>845685380</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>df12@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucas Costa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1576281713</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>df32@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>X^743816816092oc</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -8870,34 +8705,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Joao </t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1371400479</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>tributario5@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Marcia Regina</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1574580894</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>df29@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>D.983222139855od</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>T#eC@1881</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -8905,220 +8742,226 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>123456</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>GTCON25?</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Lucas Costa</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>1576281713</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>df32@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Maria Leticia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1583340780</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>df28@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>V(846343661424aw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rafael Sigolo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1102924583</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>df10@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>T#eC@1881</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IMPLANTAÇÃO CONTÁBIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>449308884</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dc2@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Teccon123#</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Joyce</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1720579671</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dc10@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>R$937248927378ow</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Marcia Regina</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1574580894</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>df29@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Luciene</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1966771201</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dc18@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25?</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Maria Leticia</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1583340780</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>df28@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F@995158738329oc</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Matheus Grego</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1077946627</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>implantacao4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>V(846343661424aw</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Rafael Sigolo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>1102924583</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>df10@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1881</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>IMPLANTAÇÃO CONTÁBIL</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Jane</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>449308884</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>dc2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>T#eC@1882</t>
         </is>
@@ -9128,34 +8971,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Teccon123#</t>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>12345678</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Joyce</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1720579671</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>dc10@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>122516579</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>dc25@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>R$937248927378ow</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>S/978065223264ov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -9165,32 +9010,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>GTCON25</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Luciene</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1966771201</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>dc18@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
+          <t xml:space="preserve">Tiago </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1835829731</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dc30@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>F@995158738329oc</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>W^893766115038at</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -9200,190 +9047,189 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Matheus Grego</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>1077946627</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>implantacao4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>12345678</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Renata</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>122516579</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>dc25@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
+          <t>IMPLANTAÇÃO DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cassia Yara</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1745878002</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dp4@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>S/978065223264ov</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiago </t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>1835829731</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>dc30@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>X(772305274330on</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>HOME OFFICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Debora</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1298981761</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dp8@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>W^893766115038at</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="1" t="n"/>
-      <c r="E22" s="1" t="n"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N.035683188113os</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>IMPLANTAÇÃO DP</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fabiana Uchoa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1566888559</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>implantacaodp@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>T#eC@1882</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E24" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Nathalya</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1603214365</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dp22@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Gtcon#2024*</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>K@716354364977ub</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Cassia Yara</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1745878002</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>dp4@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Thaiana</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1244659823</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>dp20@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>X(772305274330on</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>P&amp;521001664494ob</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -9391,69 +9237,73 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>HOME OFFICE</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GTCON25</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Debora</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1298981761</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>dp8@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>N.035683188113os</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aline</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1101857679</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nit6@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PESSOAL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>H&amp;832207924445ad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
+          <t>OK- SERVIDOR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fabiana Uchoa</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>1566888559</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>implantacaodp@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
+          <t xml:space="preserve">Tatiana Santos </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1229136097</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>dp18@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>T#eC@1882</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>H/028227961485uf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9461,34 +9311,36 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>GTCON25?</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nathalya</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1603214365</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>dp22@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
+          <t>Ronilson</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1668313085</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>dp19@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Gtcon#2024*</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>K@716354364977ub</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>M*408552573824ud</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9496,175 +9348,13 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Thaiana</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1244659823</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>dp20@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>P&amp;521001664494ob</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>GTCON25</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Aline</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1101857679</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>nit6@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>PESSOAL</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>H&amp;832207924445ad</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>OK- SERVIDOR</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tatiana Santos </t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1229136097</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>dp18@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>H/028227961485uf</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25?</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Ronilson</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1668313085</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>dp19@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>M*408552573824ud</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>GTCON25</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" display="mailto:df10@grupoteccon.com.br" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" display="mailto:implantacao4@grupoteccon.com.br" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" display="mailto:dp8@grupoteccon.com.br" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId14"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Controle_/Acessos GTCON.xlsx
+++ b/Controle_/Acessos GTCON.xlsx
@@ -3442,70 +3442,90 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor theme="0" tint="-0.3499862666707358"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="38.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="24.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="9.7109375" bestFit="1" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>COMERCIAL</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>COLABORADOR</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ANYDESK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SENHA PADRAO ANYDESK</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ONEDRIVE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CERTIFICADO GTCON</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAQUINA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
-        <is>
-          <t>COLABORADOR</t>
-        </is>
-      </c>
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>ANYDESK</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="inlineStr">
-        <is>
-          <t>E-MAIL</t>
-        </is>
-      </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>SENHA PADRÃO ANYDESK</t>
-        </is>
-      </c>
-      <c r="E2" s="27" t="inlineStr">
-        <is>
-          <t>ONEDRIVE</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>CERTIFICADO GTCON</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>MAQUINA</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ayrton</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ayrtonjunior@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>V#254258672703ol</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NÃO UTILIZA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ayrton</t>
+          <t xml:space="preserve">Daniel </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3515,7 +3535,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ayrtonjunior@gtconbrasil.com.br</t>
+          <t>comercial1@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3523,9 +3543,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>V#254258672703ol</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K*227143754197op</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3533,7 +3553,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3542,7 +3562,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daniel </t>
+          <t>Ellen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3552,7 +3572,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>comercial1@gtconbrasil.com.br</t>
+          <t>ellen@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3562,7 +3582,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>K*227143754197op</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3570,7 +3590,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3579,7 +3599,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ellen</t>
+          <t>Felipe Rodrigues</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3589,7 +3609,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ellen@gtconbrasil.com.br</t>
+          <t>comercial@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3599,7 +3619,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t xml:space="preserve">K%886307565079ur </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3607,7 +3627,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3616,7 +3636,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Felipe Rodrigues</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3626,7 +3646,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>comercial@gtconbrasil.com.br</t>
+          <t>fernandosantos@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3634,9 +3654,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K%886307565079ur </t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3644,7 +3664,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3653,27 +3673,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Kaique</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1543419339</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fernandosantos@gtconbrasil.com.br</t>
+          <t>comercial2@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Gtcon#2024*</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>T@881445245502ag</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3681,7 +3701,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3690,25 +3710,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kaique</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1543419339</v>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>comercial2@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Gtcon#2024*</t>
+          <t>marco@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T@881445245502ag</t>
+          <t>L&amp;085495255261os</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3716,7 +3738,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3725,7 +3747,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marco</t>
+          <t>Mauricio</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3735,7 +3757,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>marco@gtconbrasil.com.br</t>
+          <t>mauriciooliveira@gtconbrasil.com.br</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3743,9 +3765,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>L&amp;085495255261os</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>F$398479054850oz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3753,7 +3775,7 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3762,7 +3784,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mauricio</t>
+          <t>Ranieri</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3772,17 +3794,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mauriciooliveira@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>F$398479054850oz</t>
+          <t>ranieri@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>M%121117676032uf</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3790,16 +3808,12 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ranieri</t>
+          <t>Walter</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3809,12 +3823,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ranieri@gtconbrasil.com.br</t>
+          <t>walter.leite@gtconbrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>M%121117676032uf</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3822,56 +3841,14 @@
           <t>NÃO UTILIZA</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Walter</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>walter.leite@gtconbrasil.com.br</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>NÃO UTILIZA</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4075,7 +4052,6 @@
           <t>Dominio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>adm.dominio@gtconbrasil.com.br</t>
@@ -4256,7 +4232,6 @@
           <t>Onvio/G-click | Integração</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>integracaogclick@gtconbrasil.com.br</t>
